--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9256988048</v>
+        <v>46157.93104168153</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93104168153</v>
+        <v>46157.93175810292</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93175810292</v>
+        <v>46157.93401454693</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401454693</v>
+        <v>46157.9371945064</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9371945064</v>
+        <v>46158.28217616866</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217616866</v>
+        <v>46158.29683630467</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29683630467</v>
+        <v>46158.29816364784</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29816364784</v>
+        <v>46158.33388698572</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388698572</v>
+        <v>46158.3685847915</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3685847915</v>
+        <v>46158.37289170828</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
